--- a/excel/pacientes_ejemplo.xlsx
+++ b/excel/pacientes_ejemplo.xlsx
@@ -413,80 +413,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TipoDocumento</t>
+          <t>paciente_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NumeroDocumento</t>
+          <t>tipo_documento</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Nombres</t>
+          <t>documento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Apellidos</t>
+          <t>nombre_completo</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>FechaNacimiento</t>
+          <t>fecha_nacimiento</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Sexo</t>
+          <t>genero</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Telefono</t>
+          <t>telefono</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>correo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Direccion</t>
+          <t>eps_codigo</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>eps_nombre</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ciudad</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fecha_creacion</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1001234567</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JUAN CARLOS</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PEREZ GOMEZ</t>
+          <t>JUAN CARLOS PEREZ GOMEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,7 +519,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,37 +529,62 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>juan.perez@email.com</t>
+          <t>juan.perez@example.test</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cra 1 #2-3 Bogota</t>
-        </is>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
+          <t>EPS001</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sanitas</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:00:00</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>1007654321</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MARIA ELENA</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ LOPEZ</t>
+          <t>MARIA ELENA RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,7 +594,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -556,37 +604,62 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>maria.rodriguez@email.com</t>
+          <t>maria.rodriguez@example.test</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Calle 5 #10-15 Medellin</t>
-        </is>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
+          <t>EPS002</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Medellin</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:05:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:05:00</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1012345678</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CARLOS ANDRES</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GOMEZ VARGAS</t>
+          <t>CARLOS ANDRES GOMEZ VARGAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,7 +669,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,37 +679,62 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>carlos.gomez@email.com</t>
+          <t>carlos.gomez@example.test</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Av Caracas #45-67 Cali</t>
-        </is>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
+          <t>EPS001</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sanitas</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Atendido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:10:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:10:00</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1023456789</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ANA LUCIA</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARTINEZ SANCHEZ</t>
+          <t>ANA LUCIA MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,7 +744,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -656,37 +754,62 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ana.martinez@email.com</t>
+          <t>ana.martinez@example.test</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Transversal 7 #23-89 Bogota</t>
-        </is>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
+          <t>EPS003</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Coosalud</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:15:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:15:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1034567890</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PEDRO JOSE</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DIAZ RAMIREZ</t>
+          <t>PEDRO JOSE DIAZ RAMIREZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,7 +819,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -706,37 +829,62 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>pedro.diaz@email.com</t>
+          <t>pedro.diaz@example.test</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Calle 12 #8-45 Bucaramanga</t>
-        </is>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
+          <t>EPS002</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>En atencion</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:20:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:20:00</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1045678901</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LAURA FERNANDA</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CASTRO MORENO</t>
+          <t>LAURA FERNANDA CASTRO MORENO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,7 +894,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -756,37 +904,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>laura.castro@email.com</t>
+          <t>laura.castro@example.test</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cra 15 #3-67 Cartagena</t>
-        </is>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
+          <t>EPS001</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sanitas</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:25:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:25:00</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1056789012</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>JORGE ENRIQUE</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LOPEZ GUERRA</t>
+          <t>JORGE ENRIQUE LOPEZ GUERRA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +969,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -806,37 +979,62 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>jorge.lopez@email.com</t>
+          <t>jorge.lopez@example.test</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Av Boyaca #56-23 Barranquilla</t>
-        </is>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
+          <t>EPS003</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Coosalud</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Atendido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:30:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:30:00</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1067890123</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PATRICIA DEL PILAR</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VEGA HERRERA</t>
+          <t>PATRICIA DEL PILAR VEGA HERRERA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,7 +1044,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,37 +1054,62 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>patricia.vega@email.com</t>
+          <t>patricia.vega@example.test</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Calle 80 #15-90 Bogota</t>
-        </is>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
+          <t>EPS002</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:35:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:35:00</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1078901234</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ALEJANDRO JOSE</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MENDOZA TORRES</t>
+          <t>ALEJANDRO JOSE MENDOZA TORRES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,7 +1119,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -906,37 +1129,62 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>alejandro.mendoza@email.com</t>
+          <t>alejandro.mendoza@example.test</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Av 80 #45-12 Medellin</t>
-        </is>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
+          <t>EPS001</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sanitas</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Medellin</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:40:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:40:00</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1089012345</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CLAUDIA PATRICIA</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORTIZ RAMOS</t>
+          <t>CLAUDIA PATRICIA ORTIZ RAMOS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,7 +1194,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -956,16 +1204,43 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>claudia.ortiz@email.com</t>
+          <t>claudia.ortiz@example.test</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Calle 100 #20-45 Bogota</t>
-        </is>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
+          <t>EPS003</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Coosalud</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:45:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-01-01 08:45:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
